--- a/Results/Study 2/Confusion Matrices (train images).xlsx
+++ b/Results/Study 2/Confusion Matrices (train images).xlsx
@@ -610,21 +610,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>299</v>
-      </c>
-      <c r="C2">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>238</v>
-      </c>
-      <c r="C3">
-        <v>402</v>
+        <v>290</v>
+      </c>
+      <c r="C2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>242</v>
+      </c>
+      <c r="C3">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -650,10 +650,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>405</v>
-      </c>
-      <c r="C2">
-        <v>235</v>
+        <v>406</v>
+      </c>
+      <c r="C2">
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:3">

--- a/Results/Study 2/Confusion Matrices (train images).xlsx
+++ b/Results/Study 2/Confusion Matrices (train images).xlsx
@@ -410,21 +410,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>479</v>
-      </c>
-      <c r="C2">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>471</v>
-      </c>
-      <c r="C3">
-        <v>169</v>
+        <v>363</v>
+      </c>
+      <c r="C2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>355</v>
+      </c>
+      <c r="C3">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -450,21 +450,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>525</v>
-      </c>
-      <c r="C2">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>500</v>
-      </c>
-      <c r="C3">
-        <v>140</v>
+        <v>527</v>
+      </c>
+      <c r="C2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>467</v>
+      </c>
+      <c r="C3">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -490,21 +490,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>224</v>
-      </c>
-      <c r="C2">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>224</v>
-      </c>
-      <c r="C3">
-        <v>416</v>
+        <v>288</v>
+      </c>
+      <c r="C2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>288</v>
+      </c>
+      <c r="C3">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -530,21 +530,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>513</v>
-      </c>
-      <c r="C2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>483</v>
-      </c>
-      <c r="C3">
-        <v>157</v>
+        <v>499</v>
+      </c>
+      <c r="C2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>412</v>
+      </c>
+      <c r="C3">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -570,21 +570,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>546</v>
-      </c>
-      <c r="C2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>516</v>
-      </c>
-      <c r="C3">
-        <v>124</v>
+        <v>517</v>
+      </c>
+      <c r="C2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>449</v>
+      </c>
+      <c r="C3">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -610,21 +610,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>290</v>
-      </c>
-      <c r="C2">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>242</v>
-      </c>
-      <c r="C3">
-        <v>398</v>
+        <v>326</v>
+      </c>
+      <c r="C2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>298</v>
+      </c>
+      <c r="C3">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -650,21 +650,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>406</v>
-      </c>
-      <c r="C2">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>291</v>
-      </c>
-      <c r="C3">
-        <v>349</v>
+        <v>428</v>
+      </c>
+      <c r="C2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>275</v>
+      </c>
+      <c r="C3">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -690,10 +690,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>548</v>
-      </c>
-      <c r="C2">
-        <v>92</v>
+        <v>538</v>
+      </c>
+      <c r="C2">
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -730,21 +730,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>475</v>
-      </c>
-      <c r="C2">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>412</v>
-      </c>
-      <c r="C3">
-        <v>228</v>
+        <v>542</v>
+      </c>
+      <c r="C2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>385</v>
+      </c>
+      <c r="C3">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -770,21 +770,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>525</v>
-      </c>
-      <c r="C2">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>512</v>
-      </c>
-      <c r="C3">
-        <v>128</v>
+        <v>557</v>
+      </c>
+      <c r="C2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>542</v>
+      </c>
+      <c r="C3">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -810,21 +810,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>495</v>
-      </c>
-      <c r="C2">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>435</v>
-      </c>
-      <c r="C3">
-        <v>205</v>
+        <v>505</v>
+      </c>
+      <c r="C2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>407</v>
+      </c>
+      <c r="C3">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -850,21 +850,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>256</v>
-      </c>
-      <c r="C2">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>256</v>
-      </c>
-      <c r="C3">
-        <v>384</v>
+        <v>320</v>
+      </c>
+      <c r="C2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>320</v>
+      </c>
+      <c r="C3">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
